--- a/Day-03 Fixed Voice Part 1/summary/D-03 Q&A.xlsx
+++ b/Day-03 Fixed Voice Part 1/summary/D-03 Q&A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Windows\Mahmoud\Course\We Training\summary\Day-03 Fixed Voice Part 1\summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F3236FC-EE35-48CC-AD3B-96FA16300968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{816D615D-D4CC-447F-BA8A-3A088A5B5CB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{7031842B-F9B2-4D73-84BA-25447A6A0798}"/>
   </bookViews>
@@ -19,6 +19,7 @@
     <definedName name="_Hlk195658349" localSheetId="0">'day 3'!$D$41</definedName>
     <definedName name="_Hlk195658424" localSheetId="0">'day 3'!$C$17</definedName>
     <definedName name="_Hlk195658445" localSheetId="0">'day 3'!$C$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'day 3'!$A$1:$N$108</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -287,15 +288,6 @@
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -306,6 +298,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1148,7 +1149,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10763347471" y="14308206"/>
+          <a:off x="10777531928" y="15649499"/>
           <a:ext cx="2181446" cy="1172973"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1722,6 +1723,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8165240E-DF17-4B82-9D84-8AE46A89FCB7}">
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:O108"/>
   <sheetFormatPr defaultColWidth="9.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1731,633 +1733,601 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="5">
+      <c r="B2" s="2">
         <v>1</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="5">
+      <c r="B7" s="2">
         <v>2</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
     </row>
     <row r="12" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="J13" s="6" t="s">
+      <c r="J13" s="3" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="17" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="5">
+      <c r="B17" s="2">
         <v>3</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
     </row>
     <row r="22" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="24" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="5">
+      <c r="B25" s="2">
         <v>4</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="J33" s="8" t="s">
+      <c r="J33" s="5" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="E34" s="2" t="s">
+      <c r="E34" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
     </row>
     <row r="35" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="36" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="5">
+      <c r="B36" s="2">
         <v>5</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
     </row>
     <row r="38" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="39" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E39" s="6" t="b">
+      <c r="E39" s="3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="41" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="5">
+      <c r="B41" s="2">
         <v>6</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
-      <c r="M41" s="4"/>
-      <c r="N41" s="4"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="6"/>
+      <c r="M41" s="6"/>
+      <c r="N41" s="6"/>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="4"/>
-      <c r="L42" s="4"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6"/>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="E44" s="2" t="s">
+      <c r="E44" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="7"/>
     </row>
     <row r="45" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="46" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="5">
+      <c r="B46" s="2">
         <v>7</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
-      <c r="K46" s="4"/>
-      <c r="L46" s="4"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
+      <c r="K46" s="6"/>
+      <c r="L46" s="6"/>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-      <c r="K47" s="4"/>
-      <c r="L47" s="4"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="6"/>
+      <c r="K47" s="6"/>
+      <c r="L47" s="6"/>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="4"/>
-      <c r="L48" s="4"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="6"/>
     </row>
     <row r="49" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="4"/>
-      <c r="L49" s="4"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6"/>
+      <c r="J49" s="6"/>
+      <c r="K49" s="6"/>
+      <c r="L49" s="6"/>
     </row>
     <row r="51" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="E51" s="2" t="s">
+      <c r="E51" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="7"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="4"/>
     </row>
     <row r="52" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="53" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="5">
+      <c r="B53" s="2">
         <v>8</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="D53" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
-      <c r="N53" s="4"/>
-      <c r="O53" s="4"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="6"/>
+      <c r="K53" s="6"/>
+      <c r="L53" s="6"/>
+      <c r="M53" s="6"/>
+      <c r="N53" s="6"/>
+      <c r="O53" s="6"/>
     </row>
     <row r="54" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="D54" s="4" t="s">
+      <c r="D54" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="4"/>
-      <c r="L54" s="4"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6"/>
+      <c r="L54" s="6"/>
     </row>
     <row r="55" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="56" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E56" s="6" t="s">
+      <c r="E56" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="57" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="58" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="5">
+      <c r="B58" s="2">
         <v>9</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="D58" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="4"/>
-      <c r="J58" s="4"/>
-      <c r="K58" s="4"/>
-      <c r="L58" s="4"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6"/>
+      <c r="K58" s="6"/>
+      <c r="L58" s="6"/>
     </row>
     <row r="59" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="D59" s="4" t="s">
+      <c r="D59" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
-      <c r="I59" s="4"/>
-      <c r="J59" s="4"/>
-      <c r="K59" s="4"/>
-      <c r="L59" s="4"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="6"/>
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6"/>
+      <c r="K59" s="6"/>
+      <c r="L59" s="6"/>
     </row>
     <row r="61" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="E61" s="2" t="s">
+      <c r="E61" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
+      <c r="F61" s="7"/>
+      <c r="G61" s="7"/>
+      <c r="H61" s="7"/>
     </row>
     <row r="62" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="63" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="5">
+      <c r="B63" s="2">
         <v>10</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="D63" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E63" s="4"/>
-      <c r="F63" s="4"/>
-      <c r="G63" s="4"/>
-      <c r="H63" s="4"/>
-      <c r="I63" s="4"/>
-      <c r="J63" s="4"/>
-      <c r="K63" s="4"/>
-      <c r="L63" s="4"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="6"/>
+      <c r="K63" s="6"/>
+      <c r="L63" s="6"/>
     </row>
     <row r="64" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="D64" s="4" t="s">
+      <c r="D64" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E64" s="4"/>
-      <c r="F64" s="4"/>
-      <c r="G64" s="4"/>
-      <c r="H64" s="4"/>
-      <c r="I64" s="4"/>
-      <c r="J64" s="4"/>
-      <c r="K64" s="4"/>
-      <c r="L64" s="4"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="6"/>
+      <c r="K64" s="6"/>
+      <c r="L64" s="6"/>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="E66" s="3" t="s">
+      <c r="E66" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F66" s="2"/>
+      <c r="F66" s="7"/>
     </row>
     <row r="67" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="68" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="5">
+      <c r="B68" s="2">
         <v>11</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="D68" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
-      <c r="H68" s="4"/>
-      <c r="I68" s="4"/>
-      <c r="J68" s="4"/>
-      <c r="K68" s="4"/>
-      <c r="L68" s="4"/>
+      <c r="E68" s="6"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="6"/>
+      <c r="I68" s="6"/>
+      <c r="J68" s="6"/>
+      <c r="K68" s="6"/>
+      <c r="L68" s="6"/>
     </row>
     <row r="69" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="D69" s="4" t="s">
+      <c r="D69" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="4"/>
-      <c r="I69" s="4"/>
-      <c r="J69" s="4"/>
-      <c r="K69" s="4"/>
-      <c r="L69" s="4"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="6"/>
+      <c r="J69" s="6"/>
+      <c r="K69" s="6"/>
+      <c r="L69" s="6"/>
     </row>
     <row r="76" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="E76" s="3" t="s">
+      <c r="E76" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F76" s="2"/>
+      <c r="F76" s="7"/>
     </row>
     <row r="77" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="78" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="5">
+      <c r="B78" s="2">
         <v>12</v>
       </c>
-      <c r="D78" s="4" t="s">
+      <c r="D78" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
-      <c r="H78" s="4"/>
-      <c r="I78" s="4"/>
-      <c r="J78" s="4"/>
-      <c r="K78" s="4"/>
-      <c r="L78" s="4"/>
-      <c r="M78" s="4"/>
-      <c r="N78" s="4"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="6"/>
+      <c r="G78" s="6"/>
+      <c r="H78" s="6"/>
+      <c r="I78" s="6"/>
+      <c r="J78" s="6"/>
+      <c r="K78" s="6"/>
+      <c r="L78" s="6"/>
+      <c r="M78" s="6"/>
+      <c r="N78" s="6"/>
     </row>
     <row r="79" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="D79" s="4" t="s">
+      <c r="D79" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4"/>
-      <c r="I79" s="4"/>
-      <c r="J79" s="4"/>
-      <c r="K79" s="4"/>
-      <c r="L79" s="4"/>
+      <c r="E79" s="6"/>
+      <c r="F79" s="6"/>
+      <c r="G79" s="6"/>
+      <c r="H79" s="6"/>
+      <c r="I79" s="6"/>
+      <c r="J79" s="6"/>
+      <c r="K79" s="6"/>
+      <c r="L79" s="6"/>
     </row>
     <row r="87" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E87" s="3" t="s">
+      <c r="E87" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F87" s="2"/>
+      <c r="F87" s="7"/>
     </row>
     <row r="88" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="89" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B89" s="5">
+      <c r="B89" s="2">
         <v>13</v>
       </c>
-      <c r="D89" s="4" t="s">
+      <c r="D89" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E89" s="4"/>
-      <c r="F89" s="4"/>
-      <c r="G89" s="4"/>
-      <c r="H89" s="4"/>
-      <c r="I89" s="4"/>
-      <c r="J89" s="4"/>
-      <c r="K89" s="4"/>
-      <c r="L89" s="4"/>
+      <c r="E89" s="6"/>
+      <c r="F89" s="6"/>
+      <c r="G89" s="6"/>
+      <c r="H89" s="6"/>
+      <c r="I89" s="6"/>
+      <c r="J89" s="6"/>
+      <c r="K89" s="6"/>
+      <c r="L89" s="6"/>
     </row>
     <row r="90" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D90" s="4" t="s">
+      <c r="D90" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E90" s="4"/>
-      <c r="F90" s="4"/>
-      <c r="G90" s="4"/>
-      <c r="H90" s="4"/>
-      <c r="I90" s="4"/>
-      <c r="J90" s="4"/>
-      <c r="K90" s="4"/>
-      <c r="L90" s="4"/>
+      <c r="E90" s="6"/>
+      <c r="F90" s="6"/>
+      <c r="G90" s="6"/>
+      <c r="H90" s="6"/>
+      <c r="I90" s="6"/>
+      <c r="J90" s="6"/>
+      <c r="K90" s="6"/>
+      <c r="L90" s="6"/>
     </row>
     <row r="92" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E92" s="3" t="s">
+      <c r="E92" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F92" s="2"/>
+      <c r="F92" s="7"/>
     </row>
     <row r="93" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="94" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B94" s="5">
+      <c r="B94" s="2">
         <v>14</v>
       </c>
-      <c r="D94" s="4" t="s">
+      <c r="D94" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E94" s="4"/>
-      <c r="F94" s="4"/>
-      <c r="G94" s="4"/>
-      <c r="H94" s="4"/>
-      <c r="I94" s="4"/>
-      <c r="J94" s="4"/>
-      <c r="K94" s="4"/>
-      <c r="L94" s="4"/>
+      <c r="E94" s="6"/>
+      <c r="F94" s="6"/>
+      <c r="G94" s="6"/>
+      <c r="H94" s="6"/>
+      <c r="I94" s="6"/>
+      <c r="J94" s="6"/>
+      <c r="K94" s="6"/>
+      <c r="L94" s="6"/>
     </row>
     <row r="95" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D95" s="4" t="s">
+      <c r="D95" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E95" s="4"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="4"/>
-      <c r="H95" s="4"/>
-      <c r="I95" s="4"/>
-      <c r="J95" s="4"/>
-      <c r="K95" s="4"/>
-      <c r="L95" s="4"/>
+      <c r="E95" s="6"/>
+      <c r="F95" s="6"/>
+      <c r="G95" s="6"/>
+      <c r="H95" s="6"/>
+      <c r="I95" s="6"/>
+      <c r="J95" s="6"/>
+      <c r="K95" s="6"/>
+      <c r="L95" s="6"/>
     </row>
     <row r="97" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E97" s="3" t="s">
+      <c r="E97" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-      <c r="H97" s="2"/>
+      <c r="F97" s="7"/>
+      <c r="G97" s="7"/>
+      <c r="H97" s="7"/>
     </row>
     <row r="98" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="99" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B99" s="5">
+      <c r="B99" s="2">
         <v>15</v>
       </c>
-      <c r="D99" s="4" t="s">
+      <c r="D99" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E99" s="4"/>
-      <c r="F99" s="4"/>
-      <c r="G99" s="4"/>
-      <c r="H99" s="4"/>
-      <c r="I99" s="4"/>
-      <c r="J99" s="4"/>
-      <c r="K99" s="4"/>
-      <c r="L99" s="4"/>
+      <c r="E99" s="6"/>
+      <c r="F99" s="6"/>
+      <c r="G99" s="6"/>
+      <c r="H99" s="6"/>
+      <c r="I99" s="6"/>
+      <c r="J99" s="6"/>
+      <c r="K99" s="6"/>
+      <c r="L99" s="6"/>
     </row>
     <row r="100" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D100" s="4" t="s">
+      <c r="D100" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E100" s="4"/>
-      <c r="F100" s="4"/>
-      <c r="G100" s="4"/>
-      <c r="H100" s="4"/>
-      <c r="I100" s="4"/>
-      <c r="J100" s="4"/>
-      <c r="K100" s="4"/>
-      <c r="L100" s="4"/>
+      <c r="E100" s="6"/>
+      <c r="F100" s="6"/>
+      <c r="G100" s="6"/>
+      <c r="H100" s="6"/>
+      <c r="I100" s="6"/>
+      <c r="J100" s="6"/>
+      <c r="K100" s="6"/>
+      <c r="L100" s="6"/>
     </row>
     <row r="108" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E108" s="3" t="s">
+      <c r="E108" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="F108" s="2"/>
-      <c r="G108" s="2"/>
-      <c r="H108" s="2"/>
-      <c r="I108" s="2"/>
+      <c r="F108" s="7"/>
+      <c r="G108" s="7"/>
+      <c r="H108" s="7"/>
+      <c r="I108" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="C18:K18"/>
-    <mergeCell ref="C25:K25"/>
-    <mergeCell ref="C26:K26"/>
-    <mergeCell ref="D36:L36"/>
-    <mergeCell ref="D2:L2"/>
-    <mergeCell ref="D3:L3"/>
-    <mergeCell ref="D7:L7"/>
-    <mergeCell ref="D8:L8"/>
-    <mergeCell ref="C17:K17"/>
-    <mergeCell ref="D46:L46"/>
-    <mergeCell ref="D47:L47"/>
-    <mergeCell ref="D48:L48"/>
-    <mergeCell ref="D49:L49"/>
-    <mergeCell ref="E51:I51"/>
-    <mergeCell ref="D37:L37"/>
-    <mergeCell ref="D42:L42"/>
-    <mergeCell ref="E44:I44"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="D63:L63"/>
-    <mergeCell ref="D64:L64"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="D68:L68"/>
-    <mergeCell ref="D54:L54"/>
-    <mergeCell ref="D58:L58"/>
-    <mergeCell ref="D59:L59"/>
-    <mergeCell ref="D95:L95"/>
-    <mergeCell ref="E97:H97"/>
-    <mergeCell ref="D69:L69"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="D79:L79"/>
-    <mergeCell ref="E87:F87"/>
-    <mergeCell ref="D89:L89"/>
     <mergeCell ref="D99:L99"/>
     <mergeCell ref="D100:L100"/>
     <mergeCell ref="E108:I108"/>
@@ -2368,9 +2338,47 @@
     <mergeCell ref="D90:L90"/>
     <mergeCell ref="E92:F92"/>
     <mergeCell ref="D94:L94"/>
+    <mergeCell ref="D95:L95"/>
+    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="D69:L69"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="D79:L79"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="D89:L89"/>
+    <mergeCell ref="D64:L64"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="D68:L68"/>
+    <mergeCell ref="D54:L54"/>
+    <mergeCell ref="D58:L58"/>
+    <mergeCell ref="D59:L59"/>
+    <mergeCell ref="D37:L37"/>
+    <mergeCell ref="D42:L42"/>
+    <mergeCell ref="E44:I44"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="D63:L63"/>
+    <mergeCell ref="D46:L46"/>
+    <mergeCell ref="D47:L47"/>
+    <mergeCell ref="D48:L48"/>
+    <mergeCell ref="D49:L49"/>
+    <mergeCell ref="E51:I51"/>
+    <mergeCell ref="C18:K18"/>
+    <mergeCell ref="C25:K25"/>
+    <mergeCell ref="C26:K26"/>
+    <mergeCell ref="D36:L36"/>
+    <mergeCell ref="D2:L2"/>
+    <mergeCell ref="D3:L3"/>
+    <mergeCell ref="D7:L7"/>
+    <mergeCell ref="D8:L8"/>
+    <mergeCell ref="C17:K17"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
+  <pageSetup paperSize="37" scale="33" fitToWidth="0" orientation="portrait" r:id="rId1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="111" max="13" man="1"/>
+  </rowBreaks>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="14" max="1048575" man="1"/>
+  </colBreaks>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>